--- a/dTorcedores.xlsx
+++ b/dTorcedores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://safbotafogo-my.sharepoint.com/personal/pedro_arruda_safbfr_com_br/Documents/BI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://safbotafogo-my.sharepoint.com/personal/pedro_arruda_safbfr_com_br/Documents/Área de Trabalho/dash-ticket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{6E5BAC07-5921-4DE6-8DB3-4CB13821CD95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25739FF7-D5E2-446B-8BC2-7E3A013B1EFF}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{6E5BAC07-5921-4DE6-8DB3-4CB13821CD95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1C7D5E7-4581-45BB-8FB8-B4BF7771AE79}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9FA2175E-FF33-48E0-B967-CF9BFD705DE4}"/>
+    <workbookView xWindow="-28920" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{9FA2175E-FF33-48E0-B967-CF9BFD705DE4}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
   <si>
     <t>ID_TORCEDOR</t>
   </si>
@@ -138,16 +138,53 @@
   </si>
   <si>
     <t>15IP</t>
+  </si>
+  <si>
+    <t>Nossa Gente</t>
+  </si>
+  <si>
+    <t>16NG</t>
+  </si>
+  <si>
+    <t>Escolhido</t>
+  </si>
+  <si>
+    <t>17ES</t>
+  </si>
+  <si>
+    <t>Acompanhante Preto</t>
+  </si>
+  <si>
+    <t>Joias do Bairro</t>
+  </si>
+  <si>
+    <t>Acompanhante Alvinegro</t>
+  </si>
+  <si>
+    <t>18AP</t>
+  </si>
+  <si>
+    <t>19JB</t>
+  </si>
+  <si>
+    <t>20AA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -170,18 +207,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{97D1EF1C-2EA1-4838-99E0-908641DFECC9}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -513,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{668F2381-1AB6-4D9B-9F57-3C2942008A45}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.6328125" bestFit="1" customWidth="1"/>
@@ -732,6 +772,76 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
